--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/CodeSystem/track</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/CodeSystem/track</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T13:18:28+00:00</t>
+    <t>2026-10-29T07:06:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:06:30+00:00</t>
+    <t>2026-10-29T08:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:26:45+00:00</t>
+    <t>2026-10-29T09:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:23:29+00:00</t>
+    <t>2026-10-29T13:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:05:39+00:00</t>
+    <t>2026-10-29T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:50:41+00:00</t>
+    <t>2026-10-29T16:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-track.xlsx
+++ b/CodeSystem-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T16:44:10+00:00</t>
+    <t>2026-10-30T09:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
